--- a/data/gravel/Specialized Diverge 4 2025.xlsx
+++ b/data/gravel/Specialized Diverge 4 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2566757-98B5-F849-BCB2-4E30D08F4E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20435A3C-E819-2940-82FB-6255FE4F9CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3760" yWindow="3300" windowWidth="25020" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34120" yWindow="-17960" windowWidth="25020" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -335,6 +335,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>https://assets.specialized.com/i/specialized/95426-11_DIVERGE-PRO-LTD-FLORED-YEL_HERO-SQUARE?$scom-plp-product-image-square$&amp;fmt=webp</t>
   </si>
 </sst>
 </file>
@@ -720,6 +723,11 @@
         <v>102</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>105</v>
+      </c>
+    </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Specialized Diverge 4 2025.xlsx
+++ b/data/gravel/Specialized Diverge 4 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20435A3C-E819-2940-82FB-6255FE4F9CD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F2226C-1CC3-1249-BAEA-C4DD832981C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34120" yWindow="-17960" windowWidth="25020" windowHeight="13560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28580" yWindow="-17900" windowWidth="30080" windowHeight="13100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
   <si>
     <t>brand</t>
   </si>
@@ -43,9 +43,6 @@
     <t>data_range</t>
   </si>
   <si>
-    <t>a8:h35</t>
-  </si>
-  <si>
     <t>frame_size</t>
   </si>
   <si>
@@ -79,9 +76,6 @@
     <t>Seatpost Length</t>
   </si>
   <si>
-    <t>bb_height</t>
-  </si>
-  <si>
     <t>seat_tube_angle</t>
   </si>
   <si>
@@ -338,6 +332,12 @@
   </si>
   <si>
     <t>https://assets.specialized.com/i/specialized/95426-11_DIVERGE-PRO-LTD-FLORED-YEL_HERO-SQUARE?$scom-plp-product-image-square$&amp;fmt=webp</t>
+  </si>
+  <si>
+    <t>frame_weight</t>
+  </si>
+  <si>
+    <t>a8:h34</t>
   </si>
 </sst>
 </file>
@@ -677,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -696,7 +696,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -720,28 +720,28 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7" t="s">
-        <v>7</v>
+      <c r="B7" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8">
         <v>49</v>
@@ -764,10 +764,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
         <v>9</v>
-      </c>
-      <c r="B9" t="s">
-        <v>10</v>
       </c>
       <c r="C9">
         <v>165</v>
@@ -790,10 +790,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B10" t="s">
         <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
       </c>
       <c r="C10">
         <v>380</v>
@@ -816,10 +816,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" t="s">
         <v>13</v>
-      </c>
-      <c r="B11" t="s">
-        <v>14</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -842,10 +842,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>14</v>
+      </c>
+      <c r="B12" t="s">
         <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
       </c>
       <c r="C12">
         <v>155</v>
@@ -868,10 +868,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
         <v>17</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
       </c>
       <c r="C13">
         <v>330</v>
@@ -894,10 +894,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14">
         <v>563</v>
@@ -920,10 +920,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B15" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15">
         <v>365</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -972,10 +972,10 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17">
         <v>70</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>85</v>
@@ -1024,10 +1024,10 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B19" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C19">
         <v>72</v>
@@ -1050,10 +1050,10 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C20">
         <v>391</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C21">
         <v>55</v>
@@ -1102,10 +1102,10 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22">
         <v>604</v>
@@ -1128,10 +1128,10 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23">
         <v>430</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C24">
         <v>1019</v>
@@ -1180,10 +1180,10 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C25">
         <v>521</v>
@@ -1206,10 +1206,10 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C26">
         <v>700</v>
@@ -1232,10 +1232,10 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C27">
         <v>400</v>
@@ -1258,10 +1258,10 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C28">
         <v>74.5</v>
@@ -1283,136 +1283,139 @@
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>19</v>
+      <c r="A29" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>48</v>
+      </c>
+      <c r="C30">
+        <v>700</v>
+      </c>
+      <c r="D30">
+        <v>700</v>
+      </c>
+      <c r="E30">
+        <v>700</v>
+      </c>
+      <c r="F30">
+        <v>700</v>
+      </c>
+      <c r="G30">
+        <v>700</v>
+      </c>
+      <c r="H30">
+        <v>700</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C31">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="D31">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="E31">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="F31">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="G31">
-        <v>700</v>
+        <v>45</v>
       </c>
       <c r="H31">
-        <v>700</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D32">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E32">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F32">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G32">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H32">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C33">
-        <v>50</v>
+        <v>152</v>
       </c>
       <c r="D33">
-        <v>50</v>
+        <v>163</v>
       </c>
       <c r="E33">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="F33">
-        <v>50</v>
+        <v>175</v>
       </c>
       <c r="G33">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="H33">
-        <v>50</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="C34">
+        <v>163</v>
+      </c>
+      <c r="D34">
+        <v>170</v>
+      </c>
+      <c r="E34">
+        <v>178</v>
+      </c>
+      <c r="F34">
+        <v>180</v>
+      </c>
+      <c r="G34">
+        <v>188</v>
+      </c>
+      <c r="H34">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
         <v>53</v>
       </c>
-      <c r="C34">
-        <v>152</v>
-      </c>
-      <c r="D34">
-        <v>163</v>
-      </c>
-      <c r="E34">
-        <v>170</v>
-      </c>
-      <c r="F34">
-        <v>175</v>
-      </c>
-      <c r="G34">
-        <v>180</v>
-      </c>
-      <c r="H34">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
+      <c r="B36" t="s">
         <v>54</v>
-      </c>
-      <c r="C35">
-        <v>163</v>
-      </c>
-      <c r="D35">
-        <v>170</v>
-      </c>
-      <c r="E35">
-        <v>178</v>
-      </c>
-      <c r="F35">
-        <v>180</v>
-      </c>
-      <c r="G35">
-        <v>188</v>
-      </c>
-      <c r="H35">
-        <v>196</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>95</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
@@ -1425,84 +1428,90 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>89</v>
+      </c>
+      <c r="B39" t="s">
         <v>98</v>
-      </c>
-      <c r="B39" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>91</v>
+        <v>55</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>57</v>
       </c>
-      <c r="B41" t="s">
-        <v>58</v>
+      <c r="B41" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>59</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>60</v>
+        <v>59</v>
+      </c>
+      <c r="B43">
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>61</v>
-      </c>
-      <c r="B44">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="B47">
+        <v>20</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48">
-        <v>20</v>
+        <v>64</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>66</v>
       </c>
+      <c r="B49">
+        <v>142</v>
+      </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>68</v>
+        <v>67</v>
+      </c>
+      <c r="B50">
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B51" t="s">
         <v>69</v>
       </c>
     </row>
@@ -1510,113 +1519,110 @@
       <c r="A52" t="s">
         <v>70</v>
       </c>
-      <c r="B52" t="s">
-        <v>71</v>
-      </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>82</v>
+        <v>81</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>83</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="B64">
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B65">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>85</v>
-      </c>
-      <c r="B66">
-        <v>1</v>
+        <v>84</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>86</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>67</v>
+        <v>85</v>
+      </c>
+      <c r="B67" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>87</v>
-      </c>
-      <c r="B68" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
@@ -1626,28 +1632,23 @@
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="B72">
+        <v>3499</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>93</v>
-      </c>
-      <c r="B73">
-        <v>3499</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>95</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>104</v>
+        <v>93</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Specialized Diverge 4 2025.xlsx
+++ b/data/gravel/Specialized Diverge 4 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42F2226C-1CC3-1249-BAEA-C4DD832981C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E142EEA-B0B7-7847-82D3-A0E0B218A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28580" yWindow="-17900" windowWidth="30080" windowHeight="13100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
   <si>
     <t>brand</t>
   </si>
@@ -338,6 +338,12 @@
   </si>
   <si>
     <t>a8:h34</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Morgan Hill, California, USA</t>
   </si>
 </sst>
 </file>
@@ -677,7 +683,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1651,6 +1657,14 @@
         <v>102</v>
       </c>
     </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B75" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Specialized Diverge 4 2025.xlsx
+++ b/data/gravel/Specialized Diverge 4 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E142EEA-B0B7-7847-82D3-A0E0B218A03A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E65D9D4-EA2E-A84D-B975-C294767A0AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -344,6 +344,24 @@
   </si>
   <si>
     <t>Morgan Hill, California, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -683,7 +701,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H75"/>
+  <dimension ref="A1:H81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1515,153 +1533,183 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>68</v>
-      </c>
-      <c r="B51" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>72</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>73</v>
+        <v>112</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>75</v>
+        <v>68</v>
+      </c>
+      <c r="B57" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>81</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>82</v>
-      </c>
-      <c r="B64">
-        <v>2</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>83</v>
-      </c>
-      <c r="B65">
-        <v>1</v>
+        <v>77</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>84</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>85</v>
-      </c>
-      <c r="B67" t="s">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>88</v>
+        <v>82</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>90</v>
+        <v>83</v>
+      </c>
+      <c r="B71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72">
-        <v>3499</v>
+        <v>84</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>92</v>
+        <v>85</v>
+      </c>
+      <c r="B73" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>93</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>107</v>
       </c>
     </row>

--- a/data/gravel/Specialized Diverge 4 2025.xlsx
+++ b/data/gravel/Specialized Diverge 4 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E65D9D4-EA2E-A84D-B975-C294767A0AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{755323FE-FD6C-304F-9426-22C7ABC77C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1578,6 +1578,9 @@
       <c r="A59" t="s">
         <v>71</v>
       </c>
+      <c r="B59">
+        <v>27.2</v>
+      </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
